--- a/MainTop/20.12.2025 имена/20.12.2025 имена_объединенно_по_штрихкоду.xlsx
+++ b/MainTop/20.12.2025 имена/20.12.2025 имена_объединенно_по_штрихкоду.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\20.12.2025 имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D9AA93-54DE-4472-9D48-7A68EBA6E384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA970B7-F49A-4DE9-A9B9-9AD5FA9EEC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
     <t>штрихкод</t>
   </si>
   <si>
-    <t>количество</t>
-  </si>
-  <si>
     <t>Термобирки Михаил</t>
   </si>
   <si>
@@ -605,6 +602,9 @@
   </si>
   <si>
     <t>OZN1302409156</t>
+  </si>
+  <si>
+    <t>Num_Copies</t>
   </si>
 </sst>
 </file>
@@ -1021,15 +1021,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -1048,10 +1048,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -1081,10 +1081,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -1158,10 +1158,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -1202,10 +1202,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -1268,10 +1268,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -1356,10 +1356,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1378,10 +1378,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C68">
         <v>2</v>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -1829,10 +1829,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -1884,10 +1884,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -2027,10 +2027,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -2071,10 +2071,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C97">
         <v>1</v>

--- a/MainTop/20.12.2025 имена/20.12.2025 имена_объединенно_по_штрихкоду.xlsx
+++ b/MainTop/20.12.2025 имена/20.12.2025 имена_объединенно_по_штрихкоду.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\20.12.2025 имена\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\20.12.2025 имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA970B7-F49A-4DE9-A9B9-9AD5FA9EEC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E521F5-EF02-419E-898E-3E83868B3F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1009,8 +1009,8 @@
   <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2082,5 +2082,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>